--- a/MsPFM/AIC8822/MsTables/20241220/WF_MEASURE_TABLE_HB_20241220_1731.xlsx
+++ b/MsPFM/AIC8822/MsTables/20241220/WF_MEASURE_TABLE_HB_20241220_1731.xlsx
@@ -61,7 +61,7 @@
     <t>R_MASK_MAX</t>
   </si>
   <si>
-    <t>#A1_ANT0</t>
+    <t>#A2_ANT0</t>
   </si>
   <si>
     <t>testmode22_2024_1210_1040.bin</t>
@@ -94,7 +94,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>#A1_ANT1</t>
+    <t>#A2_ANT1</t>
   </si>
   <si>
     <t>RF2.8</t>
